--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_02_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_02_21_Cau.xlsx
@@ -731,7 +731,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>0.708</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
@@ -745,7 +749,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính precision tại từng rank relevant, lấy AP từng query rồi mới lấy mean.</t>
+          <t>Mean Average Precision (MAP): Query 1 relevant tại rank 1 và 3 =&gt; AP1 = (1/1 + 2/3) / 2 = (5/3) / 2 = 5/6 ≈ 0,8333. Query 2 relevant tại rank 2 và 3 =&gt; AP2 = (1/2 + 2/3) / 2 = (7/6) / 2 = 7/12 ≈ 0,5833. MAP = (5/6 + 7/12) / 2 = 17 / 24 ≈ 0,7083, làm tròn 3 chữ số là 0,708.</t>
         </is>
       </c>
     </row>
@@ -833,7 +837,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thành phần nào không phụ thuộc detector hiện có?</t>
+          <t>Mẫu lấy vết (mixed trace sample) để vừa tìm lỗi chưa biết vừa phủ rủi ro đã biết gồm: (a) Lưu lượng ngẫu nhiên theo tỷ lệ cố định (để phát hiện lỗi chưa biết), (b) đại diện các nhóm truy vấn phổ biến, (c) các trường hợp bất thường và cờ cảnh báo tự động, (d) phản hồi tiêu cực từ người dùng.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1231,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
@@ -1241,7 +1249,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trừ chance agreement ở tử và chia cho dư địa còn lại.</t>
+          <t>Cohen's Kappa: κ = (p_o - p_e) / (1 - p_e) = (0,80 - 0,50) / (1 - 0,50) = 0,30 / 0,50 = 0,6.</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1385,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mọi claim trong expected answer phải truy được về evidence nào?</t>
+          <t>Các trường bắt buộc để một ca kiểm thử trở thành golden record có thể kiểm toán: (a) Stable case ID bất biến, (b) câu hỏi và hành vi kỳ vọng được chuyên gia phê duyệt, (c) trích dẫn nguồn bằng chứng chính xác (provenance), (d) siêu dữ liệu về độ khó, mức độ rủi ro.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_02_21_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_14_Full_126_Cau/Day_14_Ngan_Hang_Phan_02_21_Cau.xlsx
@@ -624,10 +624,28 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Similarity là screening signal, không phải truth oracle.
-Phân tích theo nguyên lý thiết kế: Similarity là screening signal, không phải truth oracle.</t>
+- 1.0đ: Phân tích và lý giải thấu đáo nghịch lý vì sao câu phủ định đảo nghĩa vẫn có Cosine Similarity &gt; 0.9 (chung chủ đề).
+- 1.0đ: Xác định đúng vai trò của Cosine Similarity chỉ là bộ lọc sơ loại (screening gate), không phải chân lý.
+- 1.0đ: Thiết lập tầng kiểm định logic NLI (Natural Language Inference) phát hiện quan hệ Contradiction vs Entailment.
+- 1.0đ: Hoàn thiện luồng quyết định phân tầng mạch lạc (Screening -&gt; NLI logic -&gt; Final Assertion).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Luồng Ra Quyết định (Decision Path) Không Đồng nhất Độ tương đồng (Similarity) với Chân lý (Truth):
+1. **Bản chất của Vấn đề Đối ngẫu (The High-Cosine Paradox)**:
+Không gian vector embedding (như OpenAI text-embedding-3 hoặc BERT) biểu diễn ngữ nghĩa theo chủ đề (topical similarity). Hai câu có cùng chủ đề nhưng đảo ngược ý nghĩa bằng từ phủ định (ví dụ: 'Chính sách này áp dụng' vs 'Chính sách này **không** áp dụng') vẫn chia sẻ 95% ngữ cảnh từ vựng xung quanh, dẫn đến điểm tương đồng Cosine Similarity &gt; 0.90. Đồng nhất Cosine Similarity cao với tính đúng đắn là một sai lầm chết người.
+2. **Thiết kế Luồng Ra Quyết định Phân tầng (Tiered Decision Pipeline)**:
+- **Bước 1: Screening Gate qua Cosine Similarity (Bộ lọc Sơ tuyển Thô)**:
+  + Nếu `cosine_similarity &lt; 0.75` -&gt; **REJECT NGAY**: Khẳng định câu trả lời lạc đề, không liên quan đến chủ đề tham chiếu.
+  + Nếu `cosine_similarity &gt;= 0.75` -&gt; **CHUYỂN TIẾP (PASS TO NEXT STAGE)**: Chỉ xác nhận câu trả lời cùng chủ đề, CHƯA ĐƯỢC PHÉP KẾT LUẬN LÀ ĐÚNG.
+- **Bước 2: NLI Contradiction / Entailment Gate (Kiểm định Mâu thuẫn Ngữ nghĩa)**:
+  + Chạy mô hình Natural Language Inference (Cross-Encoder NLI model) kiểm tra quan hệ logic giữa Candidate và Reference:
+    * Nếu quan hệ là `Contradiction` (như Candidate B bị đảo nghĩa bằng phủ định) -&gt; **FAIL / REJECT LẬP TỨC** (mặc dù cosine &gt; 0.9).
+    * Nếu quan hệ là `Entailment` (như Candidate A diễn giải lại chính xác) -&gt; **PASS TIẾP**.
+- **Bước 3: LLM Judge / Rule Assertion Gate (Xác minh Chi tiết Cuối cùng)**:
+  + Đối soát các thực thể số, điều kiện loại trừ cụ thể. Nếu pass cả Bước 2 và Bước 3, câu trả lời mới chính thức được phê duyệt là ĐÚNG (TRUTH).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Phân biệt giữa Độ Tương đồng và Chân lý (Similarity is a Screening Signal, not a Truth Oracle): Cosine Similarity của vector embedding chỉ phản ánh sự gần gũi về mặt chủ đề không gian, không có năng lực suy luận logic mệnh đề. Một luồng thẩm định đúng chuẩn kỹ nghệ phải coi Cosine Similarity là bộ lọc sơ loại rẻ tiền ở cửa ngõ, và bắt buộc phải sử dụng các mô hình suy diễn logic (NLI / LLM Judge) ở các tầng tiếp theo để phát hiện các bẫy phủ định và sai lệch bản chất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Nils Reimers &amp; Iryna Gurevych: Sentence-BERT (EMNLP 2019) &amp; RAG Triad Evaluation Methodology</t>
         </is>
       </c>
     </row>
@@ -710,10 +728,30 @@
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Có hai failure candidate độc lập cần tách.
-Phân tích theo nguyên lý thiết kế: Có hai failure candidate độc lập cần tách.</t>
+- 1.0đ: Trình bày chuẩn xác cơ chế tính điểm của Ragas Answer Relevance qua kỹ thuật sinh câu hỏi ngược.
+- 1.0đ: Chỉ rõ lỗi thực tế từ phía ứng dụng (trả lời lạc đề sang đổi ngày thay vì hủy).
+- 1.0đ: Chỉ rõ lỗi ảo giác nghiêm trọng từ phía mô hình giám khảo (evaluator hallucination sinh sai câu hỏi ngược).
+- 1.0đ: Đưa ra kết luận phân bổ trách nhiệm kỹ thuật chuẩn xác và biện pháp hiệu chuẩn lại evaluator.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Phân bổ Trách nhiệm (Attribution) khi Điểm Ragas Answer Relevance Thấp:
+1. **Cơ chế Tính toán của Ragas Answer Relevance**:
+- Metric này đo lường xem câu trả lời có giải quyết trực tiếp câu hỏi ban đầu hay không thông qua kỹ thuật 'Reverse Question Generation': Sử dụng một mô hình LLM Evaluator đọc câu trả lời của ứng dụng (Answer) và yêu cầu tự suy đoán ngược lại xem câu hỏi ban đầu là gì (Generated Question). Sau đó, tính toán Cosine Similarity giữa Câu hỏi Gốc và Câu hỏi Được Tạo Ngược.
+2. **Bóc tách Hai Nguồn Gốc Gây Ra Điểm Thấp (Disentangling Two Causes)**:
+- **Nguyên nhân 1: Generator Irrelevance (Lỗi từ Ứng dụng AI)**:
+  + Thực tế: Câu hỏi gốc hỏi 'thủ tục hủy', nhưng câu trả lời của ứng dụng lại nói chi tiết về 'thủ tục đổi ngày bay'. Ứng dụng thực sự trả lời lạc đề.
+  + Trách nhiệm: Thuộc về **Model Generator** (bị sai lệch ý định người dùng).
+- **Nguyên nhân 2: Evaluator Hallucination (Lỗi từ Giám khảo Đánh giá)**:
+  + Đề bài nêu: Câu trả lời thực tế nói về 'đổi ngày', nhưng LLM Evaluator lại bị ảo giác (hallucination), sinh ngược ra câu hỏi là 'hỏi thủ tục hủy'!
+  + Hậu quả: Vì câu hỏi ngược sinh ra vô tình trùng với câu hỏi gốc, Cosine Similarity đáng lẽ phải rất cao, nhưng hệ thống lại ghi nhận điểm Relevance thấp.
+3. **Phân bổ Trách nhiệm Kỹ thuật Chính xác (Final Attribution)**:
+- **Đây là một ca LỖI KÉP BẤT ĐỒNG (Compound Failure)**:
+  + Về mặt bản chất sản phẩm: Ứng dụng AI có lỗi nghiệp vụ thực sự (nói lạc đề từ hủy sang đổi ngày).
+  + Về mặt đo lường đánh giá: **Công cụ chấm điểm Ragas Evaluator đã bị hỏng độ tin cậy đo lường (Measurement Failure)**. Giám khảo không đọc hiểu đúng nội dung câu trả lời mà tự bịa ra câu hỏi ngược. Điểm số thấp ghi nhận được là do sai lệch trong thuật toán sinh câu hỏi ngược của Evaluator, chứ không phản ánh đúng logic đo lường chuẩn mực.
+- **Hành động khắc phục**: Cần cô lập và calibrate lại mô hình LLM Evaluator (sử dụng model mạnh hơn như GPT-4o và kiểm tra embedding ngược), đồng thời sửa prompt của Agent để trả lời đúng câu hỏi hủy vé.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Phân định Trách nhiệm Đo lường (Metric Attribution &amp; Evaluator Validation): Khi một chỉ số đánh giá tự động (như Ragas Answer Relevance) báo điểm thấp, kỹ sư không thể mặc định quy kết là do ứng dụng. Bản thân các mô hình LLM-as-a-Judge cũng là mô hình xác suất và hoàn toàn có thể bị ảo giác (evaluator hallucination). Bóc tách giữa lỗi của hệ thống được đo (System Under Test) và lỗi của thiết bị đo (Measurement Tooling) là yêu cầu tối quan trọng của QA.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+RAGAS: Automated Evaluation of Retrieval Augmented Generation (https://docs.ragas.io/en/stable/concepts/metrics/answer_relevance.html)</t>
         </is>
       </c>
     </row>
@@ -780,10 +818,33 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Precision chỉ được lấy tại rank có relevant item.
-Phân tích theo nguyên lý thiết kế: Precision chỉ được lấy tại rank có relevant item.</t>
+- 1.0đ: Tính đúng Precision tại các rank của Q1 và tính đúng AP(Q1) = 2.6 / 3 $\approx 0.867$.
+- 1.0đ: Tính đúng Precision tại các rank của Q2 và tính đúng AP(Q2) = 1.5 / 2 = 0.750.
+- 1.0đ: Tính đúng Mean Average Precision (MAP) = (0.867 + 0.750) / 2 $\approx 0.808$ (làm tròn 3 chữ số).
+- 1.0đ: Phân tích chuẩn xác giả định nhị phân của MAP và so sánh giới hạn đối với Graded Relevance / NDCG.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Average Precision (AP) cho từng Query và MAP:
+- **Quy ước bài toán**: Độ liên quan nhị phân (Binary relevance: tài liệu liên quan có giá trị 1, không liên quan có giá trị 0).
+- **Query 1 (Q1)**: Có tổng cộng $R_1 = 3$ tài liệu liên quan, xuất hiện tại các vị trí xếp hạng (ranks): 1, 2, 5.
+  + Tại rank 1: Precision@1 = 1 / 1 = 1.000
+  + Tại rank 2: Precision@2 = 2 / 2 = 1.000
+  + Tại rank 5: Precision@5 = 3 / 5 = 0.600
+  + **Tính AP(Q1)**:
+    $$\text{AP}(Q_1) = \frac{1.000 + 1.000 + 0.600}{3} = \frac{2.600}{3} \approx \mathbf{0.867}$$
+- **Query 2 (Q2)**: Có tổng cộng $R_2 = 2$ tài liệu liên quan, xuất hiện tại các vị trí xếp hạng (ranks): 1, 4.
+  + Tại rank 1: Precision@1 = 1 / 1 = 1.000
+  + Tại rank 4: Precision@4 = 2 / 4 = 0.500
+  + **Tính AP(Q2)**:
+    $$\text{AP}(Q_2) = \frac{1.000 + 0.500}{2} = \frac{1.500}{2} = \mathbf{0.750}$$
+- **Tính Mean Average Precision (MAP)**:
+  $$\text{MAP} = \frac{\text{AP}(Q_1) + \text{AP}(Q_2)}{2} = \frac{0.8667 + 0.7500}{2} = \frac{1.6167}{2} \approx \mathbf{0.808}$$
+2. Giả định về Độ liên quan (Relevance Assumption) và Giới hạn Kỹ thuật:
+- **Giả định Nhị phân Tuyệt đối (Binary Relevance Assumption)**: MAP giả định một tài liệu chỉ có 2 trạng thái: hoàn toàn liên quan (1) hoặc hoàn toàn vô dụng (0).
+- **Giới hạn**: Trong thực tế tìm kiếm hiện đại và RAG, độ liên quan có tính phân cấp (graded relevance: cực kỳ hữu ích, hữu ích một phần, thông tin bổ trợ). MAP coi mọi tài liệu liên quan có giá trị ngang nhau, không đo lường được mức độ sâu sắc của thông tin như chỉ số NDCG (Normalized Discounted Cumulative Gain).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mean Average Precision (MAP) là thước đo tiêu chuẩn vàng kinh điển trong ngành Truy xuất Thông tin (Information Retrieval). MAP thưởng điểm rất cao cho các hệ thống đưa tài liệu liên quan lên các vị trí đầu tiên của danh sách kết quả. Tuy nhiên, điểm mù cốt tử của MAP là giả định nhị phân (binary relevance), khiến nó không phản ánh được sự khác biệt giữa một tài liệu trả lời trực tiếp câu hỏi và một tài liệu chỉ nhắc thoáng qua.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Christopher D. Manning, Prabhakar Raghavan, Hinrich Schütze: Introduction to Information Retrieval (Chapter 8: Evaluation in information retrieval, Cambridge University Press)</t>
         </is>
       </c>
     </row>
@@ -868,10 +929,26 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nếu bỏ random, unknown coverage bị phụ thuộc detector cũ.
-Phân tích theo nguyên lý thiết kế: Nếu bỏ random, unknown coverage bị phụ thuộc detector cũ.</t>
+- 1.0đ: Phân bổ ngân sách mẫu hợp lý (50% cho rủi ro đã biết và 50% cho khám phá lỗi mới).
+- 1.0đ: Thiết kế chi tiết các nhóm lấy mẫu rủi ro (negative feedback, timeouts, tail latency/high cost).
+- 1.0đ: Thiết kế phương pháp lấy mẫu khám phá thông minh (Semantic Clustering diversity sampling + uniform random).
+- 1.0đ: Nêu rõ cơ chế phát hiện các lỗi âm thầm (silent failures) từ tập mẫu khám phá.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Chiến lược Lấy mẫu 2.000 Trace (Sampling Strategy) cân bằng giữa Khám phá Lỗi mới (Discovery) và Bao phủ Rủi ro đã biết (Risk Coverage):
+1. **Phân bổ Ngân sách Mẫu (2.000 Traces Allocation)**:
+- **Nhóm 1: Bao phủ Rủi ro Đã biết (Targeted Risk Coverage - 1.000 Traces = 50%)**:
+  + 400 traces: Toàn bộ các ca có phản hồi tiêu cực từ người dùng (`user_thumbs_down == true` hoặc `user_reported_bug == true`).
+  + 300 traces: Các ca gặp lỗi kỹ thuật rõ ràng hoặc timeout (`status_code &gt;= 500` hoặc `is_timeout == true`).
+  + 300 traces: Các ca có độ trễ đuôi bất thường hoặc chi phí token cao đột biến (`latency &gt; P99` hoặc `tokens &gt; 4.000`).
+- **Nhóm 2: Khám phá Lỗi Mới chưa biết (Unknown-Unknowns Discovery - 1.000 Traces = 50%)**:
+  + 600 traces: Lấy mẫu phân tầng theo cụm ngữ nghĩa người dùng (Semantic Clustering / Diversity Sampling). Gom 1 triệu trace thành 20 cụm chủ đề; lấy ngẫu nhiên 30 trace từ mỗi cụm để đảm bảo bao phủ toàn bộ các miền kiến thức đa dạng.
+  + 400 traces: Lấy mẫu ngẫu nhiên đồng đều (Uniform Random Sampling) trên toàn bộ lưu lượng sản xuất bình thường (HTTP 200) để phát hiện các ca 'lỗi âm thầm' (silent failures mà người dùng không bấm report).
+2. **Quy trình Khám phá và Chẩn đoán (Discovery Workflow)**:
+- 1.000 trace thuộc Nhóm 2 được đưa qua mô hình phân tích bất thường không giám sát (Unsupervised Anomaly Detection) tìm kiếm các chuỗi tool call kỳ lạ hoặc phân phối token dị biệt để phát hiện sớm các failure mode mới chưa từng có trong từ điển lỗi.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Lấy mẫu Quan sát Đa mục tiêu (Dual-objective Sampling Strategy): Nếu chỉ lấy mẫu theo các lỗi đã biết (như timeout hay thumbs-down), đội ngũ QA sẽ rơi vào 'cạm bẫy thiên vị xác nhận' (confirmation bias) - chỉ thấy những gì mình đã biết tìm kiếm. Để phát hiện các lỗi mới tinh vi (như trả lời sai logic nhưng vẫn 200 OK và người dùng im lặng bỏ đi), bắt buộc phải dành 50% ngân sách mẫu cho phương pháp lấy mẫu phân tầng đa dạng ngữ nghĩa (Diversity Sampling) và ngẫu nhiên.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Collector Tail Sampling &amp; Hamel Husain: Evaluation &amp; Monitoring for LLM Applications in Production</t>
         </is>
       </c>
     </row>
@@ -998,10 +1075,27 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Không gom chỉ vì metric hay symptom giống nhau.
-Phân tích theo nguyên lý thiết kế: Không gom chỉ vì metric hay symptom giống nhau.</t>
+- 1.0đ: Xây dựng chuẩn xác Danh mục Trục 1 (Knowledge Retrieval Axis) từ empty retrieval và stale chunk.
+- 1.0đ: Xây dựng chuẩn xác Danh mục Trục 2 (Model Generation/Hallucination Axis) từ unsupported answer và wrong citation.
+- 1.0đ: Bảo vệ lập luận hợp nhất (Merge defense) dựa trên cùng bản chất nguồn gốc dữ liệu và team phụ trách.
+- 1.0đ: Bảo vệ lập luận phân tách (Split defense) kiên quyết không gộp lỗi suy luận mô hình với lỗi dữ liệu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Cây Phân loại Nguyên nhân Trục (Axial Root-Cause Coding) và Lập luận Hợp nhất/Phân tách (Merge/Split Defense):
+1. **Tạo Danh mục Trục (Axial Categories) từ 4 Mã Mở (Open Codes trên 30 trace)**:
+- Bốn mã mở ban đầu gồm: `empty retrieval`, `stale chunk`, `unsupported answer`, và `wrong citation`.
+- **Danh mục Trục 1: Trục Lỗi Truy xuất Tri thức (Knowledge Retrieval Deficiency Axis)**:
+  Bao gồm hai mã mở: `empty retrieval` và `stale chunk`.
+  *Căn nguyên chung*: Đều xuất phát từ tầng dữ liệu và công cụ tìm kiếm ngữ nghĩa (Retriever &amp; Vector Database) - dữ liệu bị thiếu hoặc tài liệu trong kho lưu trữ đã lỗi thời không được cập nhật.
+- **Danh mục Trục 2: Trục Lỗi Suy luận &amp; Ảo giác Mô hình (Model Generation &amp; Hallucination Axis)**:
+  Bao gồm hai mã mở: `unsupported answer` và `wrong citation`.
+  *Căn nguyên chung*: Đều xuất phát từ tầng suy luận của LLM Generator - mô hình tự bịa đặt khẳng định không có căn cứ hoặc gắn nhầm nguồn trích dẫn dù context có thể vẫn đầy đủ.
+2. **Bảo vệ Quyết định Hợp nhất và Phân tách (Merge / Split Defense)**:
+- **Bảo vệ việc HỢP NHẤT (Merge Defense)**: Hợp nhất `empty retrieval` và `stale chunk` vào chung một trục Retrieval vì cả hai đều có cùng đội ngũ chịu trách nhiệm (RAG / Data Engineering Team) và cùng được khắc phục bằng việc làm sạch index/cập nhật crawler dữ liệu.
+- **Bảo vệ việc PHÂN TÁCH (Split Defense)**: Tuyệt đối **KHÔNG ĐƯỢC GỘP** `unsupported answer` chung với `stale chunk`. Mặc dù biểu hiện bên ngoài đều là câu trả lời sai, nhưng một bên là do tri thức đầu vào bị hỏng (Data flaw), còn một bên là do năng lực suy luận của mô hình bị ảo giác (Reasoning flaw). Việc phân tách giúp gán đúng trách nhiệm và giải pháp kỹ thuật riêng biệt.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phương pháp Mã hóa Trục (Axial Coding in Qualitative Failure Analysis): Mã hóa mở (Open coding) chỉ thu thập các triệu chứng bề mặt. Mã hóa trục gom các triệu chứng đó lại xung quanh các trục nguyên nhân cốt lõi (Core Causal Axes). Nguyên tắc vàng của việc Merge/Split danh mục là: gom nhóm theo cơ chế gây lỗi và đội ngũ chịu trách nhiệm khắc phục (Actionable Ownership), tránh gộp cơ học theo cảm tính làm lẫn lộn giữa lỗi dữ liệu (Data Pipeline) và lỗi mô hình (Model Hallucination).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Juliet Corbin &amp; Anselm Strauss: Basics of Qualitative Research: Techniques and Procedures for Developing Grounded Theory (Axial Coding)</t>
         </is>
       </c>
     </row>
@@ -1080,10 +1174,29 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Định nghĩa phải dẫn reviewer tới cùng decision.
-Phân tích theo nguyên lý thiết kế: Định nghĩa phải dẫn reviewer tới cùng decision.</t>
+- 1.0đ: Định nghĩa vận hành rõ ràng, có tiêu chí kiểm chứng cho Wrong Tool Selection.
+- 1.0đ: Định nghĩa vận hành rõ ràng, có tiêu chí kiểm chứng cho Wrong Tool Payload/Schema.
+- 1.0đ: Định nghĩa vận hành rõ ràng, có tiêu chí kiểm chứng cho Provider Timeout/Network Error.
+- 1.0đ: Thiết lập quy tắc xử lý trường hợp một trace chứa hai lỗi (multi-labeling kèm quy tắc xác định primary root cause).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Định nghĩa Vận hành Chuẩn mực (Operational Definitions) cho Ba Loại Lỗi Bị Trộn lẫn:
+- **Loại 1: Wrong Tool Selection (Lỗi Chọn Sai Công cụ)**:
+  + *Định nghĩa vận hành*: Xảy ra khi Agent kích hoạt một công cụ $T_{\text{called}}$ mà chức năng của nó không phù hợp hoặc vi phạm ý định nghiệp vụ của prompt (ví dụ: người dùng yêu cầu tra cứu thời tiết nhưng Agent lại gọi công cụ chuyển tiền).
+  + *Tiêu chí kiểm chứng*: Tham số truyền vào có thể hợp lệ với tool đó, nhưng bản thân `tool_name` bị sai lệch.
+- **Loại 2: Wrong Tool Payload / Arguments (Lỗi Sai Tham số Đầu vào)**:
+  + *Định nghĩa vận hành*: Xảy ra khi Agent chọn đúng công cụ $T$, nhưng các tham số (arguments) truyền vào vi phạm JSON Schema của công cụ (sai kiểu dữ liệu, thiếu trường bắt buộc) hoặc sai giá trị logic (ví dụ: truyền ngày bay trong quá khứ).
+  + *Tiêu chí kiểm chứng*: Lỗi phát sinh ngay tại khâu Schema Validator trước hoặc trong khi công cụ thực thi.
+- **Loại 3: Provider Timeout / Network Failure (Lỗi Hạ tầng Nhà cung cấp)**:
+  + *Định nghĩa vận hành*: Xảy ra khi Agent chọn đúng công cụ, truyền đúng tham số hợp lệ 100%, nhưng hạ tầng API bên ngoài của công cụ bị sập, từ chối kết nối (HTTP 502/503), hoặc quá thời gian chờ kết nối (`duration &gt; timeout_threshold`).
+  + *Tiêu chí kiểm chứng*: Lỗi đến từ mã trạng thái mạng hoặc exception kết nối, không phải lỗi suy luận của Agent.
+2. Xử lý Trace có Đồng thời Hai Lỗi (Multi-error Trace Handling Contract):
+- Áp dụng nguyên tắc **Thứ bậc Nhân quả &amp; Gắn Đa Nhãn (Causal Hierarchy with Multi-labeling)**:
+  + Nếu Trace vừa chọn sai công cụ vừa bị timeout: Hệ thống cho phép gán cả hai nhãn mảng `labels = ['WRONG_TOOL', 'PROVIDER_TIMEOUT']`.
+  + **Xác định Primary Root Cause**: Gán `primary_cause = 'WRONG_TOOL'` dựa trên thứ tự xuất hiện thời gian (Temporal precedence) - việc chọn sai công cụ diễn ra trước, việc timeout sau đó chỉ là hệ quả thứ cấp khi gọi vào một endpoint không mong muốn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Định nghĩa Vận hành (Operational Definitions in Taxonomy): Một nhãn mơ hồ như 'Tool Failure' là vô dụng đối với kỹ sư sửa lỗi, vì nó gộp chung lỗi trí tuệ của mô hình (chọn sai tool), lỗi định dạng dữ liệu (sai schema), và lỗi sập mạng của đối tác bên ngoài (timeout). Định nghĩa vận hành rõ ràng và có cơ chế xử lý đa lỗi (Primary Root Cause vs Secondary Symptoms) giúp gán đúng bug cho đúng người sửa.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+ISO/IEC 25010 Systems and Software Quality Requirements and Evaluation &amp; Google SRE Incident Taxonomy</t>
         </is>
       </c>
     </row>
@@ -1162,10 +1275,24 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Saturation luôn đi kèm scope của sampling.
-Phân tích theo nguyên lý thiết kế: Saturation luôn đi kèm scope của sampling.</t>
+- 1.0đ: Đưa ra quyết định dứt khoát: Tiếp tục lấy mẫu, không được dừng lại dựa trên bão hòa ảo.
+- 1.0đ: Phân tích sâu sắc sự thiếu sót của Safety slice (chỉ có 2 trace, zero adversarial cases).
+- 1.0đ: Vạch trần cạm bẫy bão hòa lý thuyết trên dữ liệu phổ thông đối với các biến cố rủi ro hiếm gặp.
+- 1.0đ: Chuyển hướng phương pháp lấy mẫu sang Red-teaming đối kháng có chủ đích để kiểm thử ranh giới.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Quyết định Vận hành Lấy mẫu (Sampling Decision: Tiếp tục hay Dừng lại):
+1. **Quyết định Chiến lược: TIẾP TỤC LẤY MẪU CÓ CHỦ ĐÍCH, KHÔNG ĐƯỢC DỪNG LẠI (Do Not Stop Sampling)**.
+- **Phân tích bối cảnh**: Mặc dù sau ba batch liên tiếp không phát hiện thêm mã mở thông thường nào mới (đạt bão hòa lý thuyết - Theoretical Saturation cho các ca phổ thông), nhưng lát cắt an toàn (Safety Slice) mới chỉ có vỏn vẹn **hai trace** và **hoàn toàn chưa có ca kiểm thử đối kháng (Zero Adversarial Cases)**.
+- **Cạm bẫy Bão hòa Ảo (Pseudo-saturation Trap)**: Sự bão hòa hiện tại chỉ là bão hòa trên tập lưu lượng 'êm đềm' thông thường (nominal distribution). Trong an toàn AI, các lỗi chí mạng (jailbreak, prompt injection, rò rỉ dữ liệu nguy hiểm) là các biến cố cực hiếm (rare events, low probability - high impact). Việc vội vàng tuyên bố dừng lấy mẫu sẽ tạo ra ảo tưởng an toàn nguy hiểm.
+2. **Chuyển đổi Phương pháp Lấy mẫu: Từ Ngẫu nhiên sang Red-Teaming có Định hướng (Targeted Adversarial Sampling)**:
+- Dừng lấy mẫu ngẫu nhiên thông thường (vì tốn kém và không sinh thêm mã lỗi an toàn).
+- Chuyển toàn bộ ngân sách sang **Lấy mẫu Tích cực / Kiểm thử Đối kháng (Active Red-teaming &amp; Adversarial Perturbation)**:
+  + Chủ động bơm 100-200 prompt đối kháng (jailbreak prompts, roleplay attack, Unicode obfuscation) nhắm thẳng vào các ranh giới chính sách an toàn.
+  + Tiếp tục quy trình mã hóa phân loại cho đến khi lát cắt an toàn đạt được sự bão hòa thực sự (không có mã lỗi an toàn mới xuất hiện ngay cả dưới áp lực tấn công đối kháng).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Bão hòa Lý thuyết trong Phân tích Dữ liệu Hiếm (Theoretical Saturation vs Rare Event Sampling): Bão hòa lý thuyết không đơn thuần là không thấy mã mới trong dữ liệu ngẫu nhiên. Đối với các miền có rủi ro bất đối xứng cực lớn như An toàn AI (Safety &amp; Security), sự vắng mặt của bằng chứng vi phạm không đồng nghĩa với bằng chứng của sự an toàn (Absence of evidence is not evidence of absence). Chỉ khi đã thử thách hệ thống qua các kịch bản đối kháng căng thẳng nhất mà không phát sinh thêm lỗ hổng mới, quá trình lấy mẫu mới được phép dừng lại.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Red Teaming Language Models to Reduce Harms (Ganguli et al., Anthropic 2022) &amp; Qualitative Research Saturation Standards</t>
         </is>
       </c>
     </row>
@@ -1280,10 +1407,28 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kappa đo consistency đã trừ chance, không đo semantic truth.
-Phân tích theo nguyên lý thiết kế: Kappa đo consistency đã trừ chance, không đo semantic truth.</t>
+- 1.0đ: Thiết lập đúng công thức Cohen's Kappa: $\kappa = (P_o - P_e) / (1 - P_e)$.
+- 1.0đ: Tính toán số học chính xác: $\kappa = 0.05 / 0.10 = 0.50$.
+- 1.0đ: Phân tích thấu đáo hiện tượng Prevalence Trap (vì sao nhãn PASS áp đảo làm $P_e$ tăng vọt lên 0.90).
+- 1.0đ: Rút ra kết luận vận hành xác đáng: không dùng $P_o$ đơn thuần cho dữ liệu mất cân bằng và cần bổ sung ca hiếm.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán Cohen's Kappa Coefficient ($\kappa$):
+- Dữ liệu bài toán:
+  + Tỷ lệ đồng thuận quan sát được thực tế (Observed Agreement): $P_o = 0.95$ ($95\%$).
+  + Tỷ lệ đồng thuận kỳ vọng do ngẫu nhiên (Expected Agreement by Chance): $P_e = 0.90$ ($90\%$).
+- **Công thức tính Cohen's Kappa**:
+  $$\kappa = \frac{P_o - P_e}{1 - P_e}$$
+- **Thay số và tính toán**:
+  $$\kappa = \frac{0.95 - 0.90}{1.00 - 0.90} = \frac{0.05}{0.10} = \mathbf{0.50}$$
+- Kết quả: Hệ số $\kappa = 0.50$, thuộc mức **Đồng thuận Trung bình (Moderate Agreement)** theo thang đo Landis &amp; Koch.
+2. Diễn giải Cạm bẫy Tỷ lệ Hiện hành (The Prevalence Trap Paradox):
+- **Bản chất của Nghịch lý**: Mặc dù hai người chấm có vẻ đồng thuận rất cao trên bề mặt ($95\%$), nhưng hệ số Kappa thực tế chỉ đạt mức trung bình ($0.50$). Đây là hiện tượng kinh điển được gọi là **Cạm bẫy Tỷ lệ Hiện hành Cao (High Prevalence Trap)**.
+- **Nguyên nhân toán học**: Do đại đa số các ca trong tập dữ liệu đều là PASS (ví dụ 95% ca là Pass và chỉ có 5% ca là Fail), hai người chấm dù chỉ nhắm mắt gán toàn bộ là PASS một cách ngẫu nhiên cũng đã có thể dễ dàng đồng thuận tới $90\%$ ($P_e = 0.90$).
+- **Ý nghĩa thực tế**: Sự đồng thuận $95\%$ thực chất phần lớn là do tính phổ biến áp đảo của nhãn PASS tạo ra, chứ không chứng minh được năng lực phân biệt tinh tế giữa Pass và Fail của hai chuyên gia. Khi có ca FAIL hiếm hoi xuất hiện, khả năng hai người bất đồng là rất lớn. Do đó, không bao giờ được dùng tỷ lệ phần trăm đồng thuận thô ($P_o$) làm thước đo độ tin cậy trong các bài toán dữ liệu mất cân bằng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nghịch lý Feinstein và Cicchetti về Cohen's Kappa (The Prevalence Paradox): Khi tỷ lệ hiện hành của một phân loại quá lớn (gần như luôn luôn PASS), xác suất đồng thuận do ngẫu nhiên ($P_e$) bị đẩy lên mức kịch trần. Điều này khiến mẫu số $(1 - P_e)$ co lại rất nhỏ, làm cho giá trị $\kappa$ giảm mạnh ngay cả khi $P_o$ rất cao. Hiểu rõ cạm bẫy này giúp kỹ sư QA không bị đánh lừa bởi con số đồng thuận 95% bề nổi và bắt buộc phải bổ sung các ca FAIL vào tập đối soát.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Jacob Cohen: A Coefficient of Agreement for Nominal Scales (1960) &amp; Feinstein &amp; Cicchetti: High agreement but low Kappa (The Prevalence Problem)</t>
         </is>
       </c>
     </row>
@@ -1416,10 +1561,51 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Link cả PDF không chứng minh từng claim cụ thể.
-Phân tích theo nguyên lý thiết kế: Link cả PDF không chứng minh từng claim cụ thể.</t>
+- 1.0đ: Thay thế link cả file PDF bằng trích dẫn đoạn văn bản gốc chính xác (exact chunk text, page, version).
+- 1.0đ: Bóc tách rõ ràng các thực thể nghiệp vụ cụ thể (số tiền chính xác, ngày tháng, điều kiện ngoại lệ).
+- 1.0đ: Thiết lập các luật kiểm thử tự động xác định (deterministic assertions: số tiền, cụm từ bắt buộc/cấm).
+- 1.0đ: Bổ sung metadata truy vết kiểm toán (auditor ID, ngày review, cơ sở pháp lý).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế lại Bản ghi Tập Dữ liệu Chuẩn mực Vàng (Auditable Golden Dataset Record Design):
+```json
+{
+  "case_id": "gold-refund-2026-088",
+  "domain": "finance_customer_support",
+  "policy_category": "flight_cancellation_refund",
+  "user_query": "Tôi đã mua vé máy bay ngày 10/10/2026 hạng Phổ thông Tiêu chuẩn với giá 3.200.000 VNĐ. Do chuyến bay bị hãng hủy trước 24 giờ, tôi có được hoàn toàn bộ tiền không hay bị trừ phí?",
+  "ground_truth_context_provenance": {
+    "document_name": "Chinh_Sach_Hoan_Huy_Ve_2026.pdf",
+    "version": "v3.2_effective_2026_01",
+    "page_number": 14,
+    "exact_chunk_text": "Điều 8.2: Trường hợp chuyến bay bị hủy do lỗi của Hãng hàng không, hành khách được quyền yêu cầu hoàn 100% giá trị vé đã thanh toán (bao gồm toàn bộ giá cước, thuế và các loại phí). Miễn trừ 100% phí hoàn vé đối với mọi hạng vé bao gồm Phổ thông Tiêu chuẩn."
+  },
+  "expected_structured_output": {
+    "refund_eligible": true,
+    "refund_percentage": 100,
+    "exact_refund_amount_vnd": 3200000,
+    "deduction_fee_vnd": 0,
+    "applicable_clause": "Điều 8.2 - Hủy chuyến do lỗi của hãng"
+  },
+  "deterministic_assertions": [
+    { "type": "contains_exact_number", "value": 3200000 },
+    { "type": "contains_phrase", "value": "miễn trừ 100% phí" },
+    { "type": "forbidden_phrase", "value": "trừ 10% phí hành chính" }
+  ],
+  "auditor_metadata": {
+    "annotator_id": "qa_specialist_07",
+    "verified_by_legal": true,
+    "last_reviewed_date": "2026-10-15"
+  }
+}
+```
+- **Các điểm cải tiến cốt lõi có thể kiểm toán (Auditable Improvements)**:
+  + **Thay thế link PDF chung chung bằng Trích dẫn Cụ thể (Exact Chunk Text &amp; Page)**: Không trỏ vào file PDF 50 trang; trích xuất nguyên văn đoạn văn bản pháp lý chính xác (trang 14, Điều 8.2) làm căn cứ chân lý bất biến.
+  + **Thay thế Answer chung bằng Cấu trúc Dữ liệu Rõ ràng**: Bóc tách rõ số tiền ($3.200.000$), tỷ lệ ($100\%$), điều kiện miễn phí ($0$ đồng) giúp các hàm test assert tự động chạy được trong tích tắc mà không phụ thuộc vào cảm tính.
+  + **Định danh Truy vết Nguồn gốc (Provenance &amp; Auditor ID)**: Lưu rõ phiên bản chính sách và người chịu trách nhiệm thẩm định pháp lý.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Thiết kế Bản ghi Golden Dataset có Thể Kiểm toán (Auditable Record Specification): Một tập test gold chỉ ghi 'câu trả lời chung chung' và đính kèm đường link tới file PDF lớn là một thảm họa kiểm thử: không ai có thể tự động chấm điểm chính xác, và khi có tranh chấp kết quả thì không thể truy vết căn cứ pháp lý nằm ở trang nào. Bản ghi chuẩn mực phải tự chứa (self-contained), bóc tách thành các trường thuộc tính có thể assert tự động, và trích dẫn chính xác từng đoạn văn bản nguyên gốc (provenance chunk) đã được phê duyệt.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Hamel Husain: Creating a Golden Dataset for LLMs (https://hamel.dev/blog/posts/evals/) &amp; Test-Driven Development Standards</t>
         </is>
       </c>
     </row>
